--- a/exports/exhibit-by-mol.xlsx
+++ b/exports/exhibit-by-mol.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Credit Recommendations by Mode " sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Credit Recommendations by Mode " sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/exports/exhibit-by-mol.xlsx
+++ b/exports/exhibit-by-mol.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Credit Recommendations by Mode " sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Credit Recommendations by Mode " sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -471,16 +471,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6575</v>
+        <v>6702</v>
       </c>
       <c r="C2" t="n">
-        <v>1736</v>
+        <v>1780</v>
       </c>
       <c r="D2" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E2" t="n">
-        <v>61.1</v>
+        <v>60.9</v>
       </c>
     </row>
     <row r="3">
@@ -490,16 +490,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2389</v>
+        <v>2435</v>
       </c>
       <c r="C3" t="n">
-        <v>848</v>
+        <v>874</v>
       </c>
       <c r="D3" t="n">
         <v>73</v>
       </c>
       <c r="E3" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
     </row>
     <row r="4">
@@ -509,16 +509,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1103</v>
+        <v>1175</v>
       </c>
       <c r="C4" t="n">
-        <v>379</v>
+        <v>394</v>
       </c>
       <c r="D4" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E4" t="n">
-        <v>10.3</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="5">
@@ -528,16 +528,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C5" t="n">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D5" t="n">
         <v>17</v>
       </c>
       <c r="E5" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="6">
@@ -585,10 +585,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C8" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D8" t="n">
         <v>6</v>
@@ -661,10 +661,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>10760</v>
+        <v>11004</v>
       </c>
       <c r="C12" t="n">
-        <v>3451</v>
+        <v>3535</v>
       </c>
       <c r="E12" t="n">
         <v>100</v>
